--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5D689CD-32C4-4B99-AAA4-7024F3E55AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C952297C-48CA-45DB-9B31-B0E67261DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$67</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="175">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -972,19 +972,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2本先取</t>
-    <rPh sb="1" eb="2">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>センシュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>完了</t>
-  </si>
-  <si>
     <t>全体の作業項目数</t>
   </si>
   <si>
@@ -997,9 +984,6 @@
   <si>
     <t>SE</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中</t>
   </si>
   <si>
     <t>SE再生</t>
@@ -1053,152 +1037,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ガードエフェクト実装</t>
-  </si>
-  <si>
     <t>全体の作業工数</t>
   </si>
   <si>
-    <t>ガードの当たり判定</t>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作成にかかる時間</t>
-  </si>
-  <si>
-    <t>キャラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キャラクターと壁の当たり判定</t>
-    <rPh sb="7" eb="8">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キャラクターと床の当たり判定</t>
-    <rPh sb="7" eb="8">
-      <t>ユカ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーベース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キャンセル</t>
-  </si>
-  <si>
-    <t>強K攻撃</t>
-    <rPh sb="0" eb="1">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>強P攻撃</t>
-    <rPh sb="0" eb="1">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中強K攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中強P攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中弱K攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>空中弱P攻撃</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>下段ガード</t>
-    <rPh sb="0" eb="2">
-      <t>ゲダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃の当たり判定</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>再生</t>
@@ -1221,13 +1063,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>時間制限</t>
-    <rPh sb="0" eb="4">
-      <t>ジカンセイゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>死亡</t>
     <rPh sb="0" eb="2">
       <t>シボウ</t>
@@ -1239,356 +1074,175 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>しゃがみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しゃがみ強K攻撃</t>
-    <rPh sb="4" eb="5">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しゃがみ強P攻撃</t>
-    <rPh sb="4" eb="5">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>キャラクターベース</t>
-  </si>
-  <si>
-    <t>しゃがみ弱K攻撃</t>
-    <rPh sb="4" eb="5">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しゃがみ弱P攻撃</t>
-    <rPh sb="4" eb="5">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱K攻撃</t>
+    <t>カメラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
     <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弱P攻撃</t>
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーと壁の当たり判定</t>
+    <rPh sb="5" eb="6">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーと壁の当たり判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーとエネミーの判定</t>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>投げる</t>
     <rPh sb="0" eb="1">
-      <t>ジャク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>勝利敗北演出</t>
-    <rPh sb="0" eb="6">
-      <t>ショウリハイボクエンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ実装</t>
-  </si>
-  <si>
-    <t>ステージ設計</t>
-  </si>
-  <si>
-    <t>対空技1</t>
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーと弾の当たり判定</t>
+    <rPh sb="6" eb="7">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーとオブジェクトの当たり判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーと弾の当たり判定</t>
+    <rPh sb="5" eb="6">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーとオブジェクトの当たり判定</t>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピストル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取得</t>
     <rPh sb="0" eb="2">
-      <t>タイクウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対空技2</t>
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間を遅くする</t>
     <rPh sb="0" eb="2">
-      <t>タイクウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイトル画面</t>
-  </si>
-  <si>
-    <t>体力</t>
-    <rPh sb="0" eb="2">
-      <t>タイリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弾</t>
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リプレイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾と武器の当たり判定</t>
     <rPh sb="0" eb="1">
       <t>タマ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド2</t>
-  </si>
-  <si>
-    <t>弾1</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド3</t>
-  </si>
-  <si>
-    <t>弾2</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド4</t>
-  </si>
-  <si>
-    <t>弾3</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド5</t>
-  </si>
-  <si>
-    <t>上段ガード</t>
-    <rPh sb="0" eb="1">
-      <t>ダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド6</t>
-  </si>
-  <si>
-    <t>常に相手の方向を向く</t>
-    <rPh sb="0" eb="1">
-      <t>ツネ</t>
-    </rPh>
     <rPh sb="2" eb="4">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ホウコウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ム</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド7</t>
-  </si>
-  <si>
-    <t>投げ(つかみ)</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カスタムコマンド8</t>
-  </si>
-  <si>
-    <t>投げの当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
       <t>ア</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh sb="8" eb="10">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カスタムコマンド9</t>
-  </si>
-  <si>
-    <t>投げ技1</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アニメーション処理</t>
-    <rPh sb="7" eb="9">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>投げ技2</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>バトル画面</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被弾＋のけぞり</t>
+    <t>ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
     <rPh sb="0" eb="2">
-      <t>ヒダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒットエフェクト実装</t>
-  </si>
-  <si>
-    <t>ステージ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒットストップの実装</t>
-    <rPh sb="8" eb="10">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー操作</t>
-  </si>
-  <si>
-    <t>音処理</t>
-    <rPh sb="0" eb="3">
-      <t>オトショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リザルト画面</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動</t>
-  </si>
-  <si>
-    <t>移動</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音実装</t>
-  </si>
-  <si>
-    <t>UI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>音量調整の処理</t>
-  </si>
-  <si>
-    <t>画面遷移</t>
-  </si>
-  <si>
-    <t>技セレクト画面</t>
-  </si>
-  <si>
-    <t>矩形と矩形の当たり判定</t>
-    <rPh sb="6" eb="7">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>UX</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>決定処理</t>
-  </si>
-  <si>
-    <t>先行入力</t>
-  </si>
-  <si>
-    <t>未着手</t>
-  </si>
-  <si>
-    <t>突進技1</t>
-  </si>
-  <si>
-    <t>突進技2</t>
-  </si>
-  <si>
-    <t>入力猶予(コマンドの成立フレーム)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立ち</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ビルドテスト</t>
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1898,7 +1552,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1969,14 +1623,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -4065,8 +3715,8 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F103)</f>
-        <v>35.75</v>
+        <f>SUM(作業工数見積もり!F3:F97)</f>
+        <v>33.25</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -4074,8 +3724,8 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!H3:H43,"完了",作業工数見積もり!F3:F43)</f>
-        <v>19.25</v>
+        <f>SUMIF(作業工数見積もり!H3:H44,"完了",作業工数見積もり!F3:F44)</f>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4091,7 +3741,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>4.0020790020790023E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4134,7 +3784,7 @@
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-3.6666666666666667E-2</v>
+        <v>-7.3888888888888893E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4151,7 +3801,7 @@
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-3.8372093023255817E-2</v>
+        <v>-7.7325581395348841E-2</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4168,7 +3818,7 @@
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-3.9379474940334128E-2</v>
+        <v>-7.9355608591885438E-2</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4252,7 +3902,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L74"/>
+  <dimension ref="B2:L70"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
@@ -4298,26 +3948,26 @@
         <v>133</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F3" s="29">
         <v>0.25</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K3" s="21">
         <f>SUM(K4,K5,K6)</f>
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:12">
@@ -4325,7 +3975,7 @@
         <v>133</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" s="29" t="s">
         <v>17</v>
@@ -4337,14 +3987,14 @@
         <v>0.25</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J4" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="K4" s="51">
-        <f>COUNTIF(E3:E72,J4)</f>
-        <v>35</v>
+      <c r="K4" s="50">
+        <f>COUNTIF(E3:E66,J4)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -4352,7 +4002,7 @@
         <v>133</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>17</v>
@@ -4364,14 +4014,14 @@
         <v>0.25</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J5" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="51">
-        <f>COUNTIF(E3:E72,J5)</f>
-        <v>32</v>
+      <c r="K5" s="50">
+        <f>COUNTIF(E3:E66,J5)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4379,7 +4029,7 @@
         <v>133</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>17</v>
@@ -4388,17 +4038,17 @@
         <v>18</v>
       </c>
       <c r="F6" s="29">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="J6" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="51">
-        <f>COUNTIF(E3:E72,J6)</f>
-        <v>3</v>
+      <c r="K6" s="50">
+        <f>COUNTIF(E3:E66,J6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:12">
@@ -4406,96 +4056,96 @@
         <v>133</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F7" s="29">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J7" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="51">
-        <f>COUNTIF(H3:H72,J7)</f>
-        <v>63</v>
-      </c>
-      <c r="L7" s="52">
+      <c r="K7" s="50">
+        <f>COUNTIF(H3:H66,J7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="51">
         <f>K7/K3</f>
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="30" t="s">
-        <v>133</v>
+      <c r="B8" s="31" t="s">
+        <v>141</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>142</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F8" s="29">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="J8" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" s="51">
-        <f>COUNTIF(H3:H72,J8)</f>
-        <v>1</v>
+      <c r="K8" s="50">
+        <f>COUNTIF(H3:H66,J8)</f>
+        <v>35</v>
       </c>
       <c r="L8" s="42">
         <f>(K8+K9)/K3</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>145</v>
-      </c>
       <c r="D9" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F9" s="29">
         <v>0.5</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="J9" s="45" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K9" s="21">
-        <f>COUNTIF(H3:H72,J9)</f>
-        <v>6</v>
+        <f>COUNTIF(H3:H66,J9)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D10" s="29" t="s">
         <v>9</v>
@@ -4507,18 +4157,18 @@
         <v>0.5</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="2:12">
       <c r="B11" s="31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>18</v>
@@ -4527,70 +4177,70 @@
         <v>1</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="J11" s="53" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>145</v>
       </c>
       <c r="K11" s="21">
-        <f>SUM(F3:F72)</f>
-        <v>35.75</v>
+        <f>SUM(F3:F66)</f>
+        <v>33.25</v>
       </c>
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F12" s="29">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K12" s="21">
         <f>8*K11</f>
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="2:12">
       <c r="B13" s="31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C13" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="29">
+        <v>3</v>
+      </c>
+      <c r="H13" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="29">
-        <v>1</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" s="53"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="2:12">
       <c r="B14" s="31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>9</v>
@@ -4602,15 +4252,15 @@
         <v>0.5</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="31" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>9</v>
@@ -4619,59 +4269,59 @@
         <v>34</v>
       </c>
       <c r="F15" s="29">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="32" t="s">
-        <v>155</v>
+      <c r="B16" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="C16" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="29">
+        <v>2.5</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="29">
+        <v>3.5</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="29">
-        <v>1</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>158</v>
-      </c>
       <c r="D18" s="29" t="s">
         <v>9</v>
       </c>
@@ -4679,18 +4329,18 @@
         <v>34</v>
       </c>
       <c r="F18" s="29">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="32" t="s">
-        <v>155</v>
+      <c r="B19" s="31" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D19" s="29" t="s">
         <v>9</v>
@@ -4699,38 +4349,38 @@
         <v>34</v>
       </c>
       <c r="F19" s="29">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>160</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F20" s="29">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>9</v>
@@ -4742,15 +4392,15 @@
         <v>0.5</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>9</v>
@@ -4762,15 +4412,15 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>9</v>
@@ -4782,15 +4432,15 @@
         <v>0.5</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>9</v>
@@ -4802,115 +4452,115 @@
         <v>0.5</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F25" s="29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F26" s="29">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F27" s="29">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F28" s="29">
+        <v>1</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="29">
         <v>0.25</v>
       </c>
-      <c r="H28" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="29">
-        <v>0.5</v>
-      </c>
       <c r="H29" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="2:8">
-      <c r="B30" s="25" t="s">
-        <v>169</v>
+      <c r="B30" s="33" t="s">
+        <v>155</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>9</v>
@@ -4922,15 +4572,15 @@
         <v>0.5</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="25" t="s">
-        <v>169</v>
+      <c r="B31" s="33" t="s">
+        <v>155</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>9</v>
@@ -4942,15 +4592,15 @@
         <v>0.5</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="33" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>9</v>
@@ -4962,15 +4612,15 @@
         <v>0.5</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="33" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>9</v>
@@ -4982,35 +4632,23 @@
         <v>0.5</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>173</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>177</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>9</v>
@@ -5022,773 +4660,203 @@
         <v>0.5</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39" s="33" t="s">
-        <v>173</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F39" s="29">
         <v>0.5</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
-      <c r="B40" s="33" t="s">
-        <v>173</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F40" s="29">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="B41" s="33" t="s">
-        <v>173</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F41" s="29">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H42" s="29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D45" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="J46" s="53"/>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H47" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F48" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>199</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F50" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F54" s="29">
-        <v>1</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F55" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="29">
-        <v>1</v>
-      </c>
-      <c r="H56" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H57" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8">
-      <c r="B58" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F58" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H58" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H59" s="29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="29">
-        <v>1</v>
-      </c>
-      <c r="H60" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="29">
-        <v>1</v>
-      </c>
-      <c r="H62" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F63" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H63" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8">
-      <c r="B64" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" s="29">
-        <v>1</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>35</v>
-      </c>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="33"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="33"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="33"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="34"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="34"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="35"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="35"/>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" s="36"/>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" s="36"/>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" s="37"/>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" s="37"/>
+      <c r="C52" s="26"/>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="B53" s="38"/>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54" s="38"/>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55" s="38"/>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="38"/>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="39"/>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" s="39"/>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59" s="39"/>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60" s="39"/>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" s="40"/>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" s="40"/>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" s="40"/>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" s="40"/>
+      <c r="C64" s="53"/>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="D65" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="29">
-        <v>1</v>
-      </c>
-      <c r="H65" s="29" t="s">
-        <v>140</v>
-      </c>
+      <c r="B65" s="32"/>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="D66" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F66" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F67" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="29" t="s">
-        <v>140</v>
-      </c>
+      <c r="B66" s="32"/>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F68" s="29">
-        <v>1</v>
-      </c>
-      <c r="H68" s="29" t="s">
-        <v>226</v>
-      </c>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F69" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H69" s="29" t="s">
-        <v>135</v>
-      </c>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="C70" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H70" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F71" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H71" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F72" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H72" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" s="21" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="H74" s="50"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H73" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H73">
-      <sortCondition ref="C2:C73"/>
+  <autoFilter ref="C2:H67" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H67">
+      <sortCondition ref="C2:C67"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D73" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D35 D39:D67" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E73" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E35 E39:E67" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H73" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H35 H39:H67" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\koukiteam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C952297C-48CA-45DB-9B31-B0E67261DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7038D3EF-3DE5-465B-BFF3-9F3EE35893AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$69</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="212">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -962,38 +962,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アルファ素材集め</t>
-    <rPh sb="4" eb="6">
-      <t>ソザイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>全体の作業項目数</t>
-  </si>
-  <si>
-    <t>BGM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BGM再生</t>
-  </si>
-  <si>
-    <t>SE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SE再生</t>
-  </si>
-  <si>
-    <t>UI素材</t>
-    <rPh sb="2" eb="4">
-      <t>ソザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>未着手</t>
@@ -1003,20 +972,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エフェクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作業中</t>
     <rPh sb="0" eb="3">
       <t>サギョウチュウ</t>
@@ -1024,103 +979,55 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>押し合い判定</t>
-    <rPh sb="0" eb="1">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ア</t>
+    <t>全体の作業工数</t>
+  </si>
+  <si>
+    <t>作成にかかる時間</t>
+  </si>
+  <si>
+    <t>未着手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企画</t>
+    <rPh sb="0" eb="2">
+      <t>キカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ・敵・ギミックの配置設計</t>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レベルデザイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様書の作成</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウショ</t>
     </rPh>
     <rPh sb="4" eb="6">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>全体の作業工数</t>
-  </si>
-  <si>
-    <t>作成にかかる時間</t>
-  </si>
-  <si>
-    <t>再生</t>
-    <rPh sb="0" eb="2">
-      <t>サイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>再生速度調整</t>
-    <rPh sb="0" eb="2">
-      <t>サイセイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ソクド</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>システム</t>
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>カメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>未着手</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>当たり判定</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミーと壁の当たり判定</t>
-    <rPh sb="5" eb="6">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーと壁の当たり判定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーとエネミーの判定</t>
-    <rPh sb="11" eb="13">
-      <t>ハンテイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1131,28 +1038,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>操作</t>
-    <rPh sb="0" eb="2">
-      <t>ソウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パンチ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>投げる</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーと弾の当たり判定</t>
-    <rPh sb="6" eb="7">
-      <t>タマ</t>
-    </rPh>
+    <t>オブジェクトとの当たり判定</t>
     <rPh sb="8" eb="9">
       <t>ア</t>
     </rPh>
@@ -1162,59 +1048,114 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーとオブジェクトの当たり判定</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミーと弾の当たり判定</t>
+    <t>殴り攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器の取得</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器投げ</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピストル撃つ</t>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡処理</t>
+    <rPh sb="0" eb="4">
+      <t>シボウショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト（銃）</t>
+    <rPh sb="6" eb="7">
+      <t>ジュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レティクル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミーベース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー検知</t>
+    <rPh sb="5" eb="7">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス管理</t>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵どうしの当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
     <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾の処理</t>
+    <rPh sb="0" eb="1">
       <t>タマ</t>
     </rPh>
-    <rPh sb="7" eb="8">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミーとオブジェクトの当たり判定</t>
-    <rPh sb="12" eb="13">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ピストル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>取得</t>
-    <rPh sb="0" eb="2">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>時間を遅くする</t>
-    <rPh sb="0" eb="2">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームマネージャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リプレイ</t>
+    <rPh sb="2" eb="4">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラ共通</t>
+    <rPh sb="3" eb="5">
+      <t>キョウツウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1234,13 +1175,426 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ダメージ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
+    <t>タイムスケールの設定</t>
+    <rPh sb="8" eb="10">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾とオブジェクトの当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器とオブジェクトの当たり判定</t>
     <rPh sb="0" eb="2">
-      <t>シボウ</t>
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクトどうしの当たり判定</t>
+    <rPh sb="10" eb="11">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経路探索（まじで余裕あれば）</t>
+    <rPh sb="0" eb="4">
+      <t>ケイロタンサク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー（武器なし）</t>
+    <rPh sb="5" eb="7">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃範囲までの移動</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー（銃持ち）</t>
+    <rPh sb="5" eb="7">
+      <t>ジュウモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>射撃場所までの移動</t>
+    <rPh sb="0" eb="2">
+      <t>シャゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの追跡</t>
+    <rPh sb="6" eb="8">
+      <t>ツイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーとの位置調整</t>
+    <rPh sb="7" eb="11">
+      <t>イチチョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾にタイムスケール設定</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾どうしの当たり判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイムスケール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動いているか判定（時間を止める）</t>
+    <rPh sb="0" eb="1">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾のエフェクト（残像みたいなやつ）</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ザンゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾撃つ処理（クールタイムや生成数・散乱の違いで武器の種類増やせる）</t>
+    <rPh sb="0" eb="2">
+      <t>タマウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>セイセイスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サンラン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾切れ</t>
+    <rPh sb="0" eb="2">
+      <t>タマギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>殴られ時のひるみ・武器ドロップ</t>
+    <rPh sb="0" eb="1">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近くの武器取得</t>
+    <rPh sb="0" eb="1">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ブキシュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットエフェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キーマウ・パッド対応（余裕あれば）</t>
+    <rPh sb="8" eb="10">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リトライ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム進行</t>
+    <rPh sb="3" eb="5">
+      <t>シンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー生成・配置</t>
+    <rPh sb="4" eb="6">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム管理</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の撃破数</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ゲキハスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リプレイの保存</t>
+    <rPh sb="5" eb="7">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイムスケール管理</t>
+    <rPh sb="7" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト（リプレイ表示⇒スコア表示）</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移・フェード</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セーブ（最高スコアとか余裕あれば）</t>
+    <rPh sb="4" eb="6">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーディオ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM再生・切り替え</t>
+    <rPh sb="3" eb="5">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果音再生</t>
+    <rPh sb="0" eb="3">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dサウンド（FPSだしあってもいいかも）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定画面（少なくとも感度設定はいるかも）</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>カンドセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材探し</t>
+    <rPh sb="0" eb="3">
+      <t>ソザイサガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果音</t>
+    <rPh sb="0" eb="3">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エフェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクトの配置</t>
+    <rPh sb="7" eb="9">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の出現位置の配置</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1398,31 +1752,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC198E0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC6600"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1440,25 +1770,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF99CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF9933FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC9900"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1477,6 +1789,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1552,7 +1906,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1586,40 +1940,29 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="12" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,6 +1970,15 @@
     <xf numFmtId="9" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -1636,16 +1988,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF9933FF"/>
+      <color rgb="FF66FFFF"/>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFFF66FF"/>
       <color rgb="FFFFFFCC"/>
-      <color rgb="FF9933FF"/>
       <color rgb="FFFF3300"/>
       <color rgb="FF33CCFF"/>
       <color rgb="FF99FF33"/>
       <color rgb="FFCC9900"/>
       <color rgb="FFFF99CC"/>
-      <color rgb="FF0099CC"/>
-      <color rgb="FFCC6600"/>
-      <color rgb="FFC198E0"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2012,11 +2364,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>5.5093555093555097E-2</v>
+        <v>5.4979253112033194E-2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2056,7 +2408,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2121,11 +2473,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-0.20444444444444446</v>
+        <v>-0.2039911308203991</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2152,11 +2504,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>-430</v>
+        <v>-431</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>-0.21395348837209302</v>
+        <v>-0.21345707656612528</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2183,11 +2535,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>-419</v>
+        <v>-420</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>-0.21957040572792363</v>
+        <v>-0.21904761904761905</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -3715,8 +4067,8 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F97)</f>
-        <v>33.25</v>
+        <f>SUM(作業工数見積もり!F3:F99)</f>
+        <v>31.75</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -3724,7 +4076,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!H3:H44,"完了",作業工数見積もり!F3:F44)</f>
+        <f>SUMIF(作業工数見積もり!H3:H47,"完了",作業工数見積もり!F3:F47)</f>
         <v>0</v>
       </c>
       <c r="D4" t="s">
@@ -3737,7 +4089,7 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
@@ -3759,7 +4111,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -3780,11 +4132,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-450</v>
+        <v>-451</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-7.3888888888888893E-2</v>
+        <v>-7.0399113082039916E-2</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3797,11 +4149,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>-430</v>
+        <v>-431</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>-7.7325581395348841E-2</v>
+        <v>-7.366589327146171E-2</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -3814,11 +4166,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>-419</v>
+        <v>-420</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>-7.9355608591885438E-2</v>
+        <v>-7.559523809523809E-2</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -3865,7 +4217,7 @@
       <c r="B24" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="30">
         <v>45631</v>
       </c>
     </row>
@@ -3873,7 +4225,7 @@
       <c r="B25" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="30">
         <v>45662</v>
       </c>
     </row>
@@ -3881,7 +4233,7 @@
       <c r="B26" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="30">
         <v>45677</v>
       </c>
     </row>
@@ -3889,7 +4241,7 @@
       <c r="B27" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="30">
         <v>45682</v>
       </c>
     </row>
@@ -3902,16 +4254,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L70"/>
+  <dimension ref="B2:L73"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.875" style="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="21"/>
     <col min="10" max="10" width="15.625" style="21" customWidth="1"/>
     <col min="11" max="11" width="33" style="21" bestFit="1" customWidth="1"/>
@@ -3921,763 +4273,688 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="27" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="2:12">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="34" t="s">
         <v>133</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J3" s="45" t="s">
-        <v>134</v>
       </c>
       <c r="K3" s="21">
         <f>SUM(K4,K5,K6)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="43"/>
+      <c r="C4" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" s="39">
+        <f>COUNTIF(E3:E68,J4)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="43"/>
+      <c r="C5" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="39">
+        <f>COUNTIF(E3:E68,J5)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K6" s="39">
+        <f>COUNTIF(E3:E68,J6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="44"/>
+      <c r="C7" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J7" s="37"/>
+      <c r="K7" s="39"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="44"/>
+      <c r="C8" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="32" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="21" t="s">
+      <c r="K8" s="39">
+        <f>COUNTIF(H3:H68,J8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="40">
+        <f>K8/K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="44"/>
+      <c r="C9" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="39">
+        <f>COUNTIF(H3:H68,J9)</f>
+        <v>33</v>
+      </c>
+      <c r="L9" s="31">
+        <f>(K9+K10)/K3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="44"/>
+      <c r="C10" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="21">
+        <f>COUNTIF(H3:H68,J10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="44"/>
+      <c r="C11" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="28">
+        <v>1</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="K12" s="21">
+        <f>SUM(F3:F68)</f>
+        <v>31.75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="45"/>
+      <c r="C13" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="28">
+        <v>2</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="K13" s="21">
+        <f>8*K12</f>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="45"/>
+      <c r="C14" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" s="38"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="45"/>
+      <c r="C15" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="28">
+        <v>3</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="38"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="45"/>
+      <c r="C16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="45"/>
+      <c r="C17" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="45"/>
+      <c r="C18" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="28">
+        <v>2.5</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="45"/>
+      <c r="C19" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="45"/>
+      <c r="C20" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="28">
+        <v>3.5</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="45"/>
+      <c r="C21" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="28">
+        <v>2.5</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="45"/>
+      <c r="C22" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="28">
+        <v>3.5</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="45"/>
+      <c r="C23" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E23" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F23" s="28">
+        <v>1</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="45"/>
+      <c r="C24" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="45"/>
+      <c r="C25" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="45"/>
+      <c r="C26" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="46"/>
+      <c r="C28" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="46"/>
+      <c r="C29" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="28">
+        <v>1</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="46"/>
+      <c r="C30" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="28">
         <v>0.25</v>
       </c>
-      <c r="H4" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J4" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="K4" s="50">
-        <f>COUNTIF(E3:E66,J4)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="50">
-        <f>COUNTIF(E3:E66,J5)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="H30" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="29">
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="46"/>
+      <c r="C31" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="28">
         <v>0.5</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="K6" s="50">
-        <f>COUNTIF(E3:E66,J6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="50">
-        <f>COUNTIF(H3:H66,J7)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="51">
-        <f>K7/K3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="29">
+      <c r="H31" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="46"/>
+      <c r="C32" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="28">
         <v>0.5</v>
       </c>
-      <c r="H8" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="K8" s="50">
-        <f>COUNTIF(H3:H66,J8)</f>
-        <v>35</v>
-      </c>
-      <c r="L8" s="42">
-        <f>(K8+K9)/K3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="H32" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="46"/>
+      <c r="C33" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="28">
         <v>0.5</v>
       </c>
-      <c r="H9" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="K9" s="21">
-        <f>COUNTIF(H3:H66,J9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="29">
+      <c r="H33" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="46"/>
+      <c r="C34" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="28">
         <v>0.5</v>
       </c>
-      <c r="H10" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="29">
-        <v>1</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J11" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="K11" s="21">
-        <f>SUM(F3:F66)</f>
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="29">
-        <v>2</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="K12" s="21">
-        <f>8*K11</f>
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="29">
-        <v>3</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="J13" s="49"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="H34" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="46"/>
+      <c r="C35" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="46"/>
+      <c r="C36" s="21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="46"/>
+      <c r="C37" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="28">
         <v>0.5</v>
       </c>
-      <c r="H14" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="29">
-        <v>1.5</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="29">
-        <v>2.5</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="29">
-        <v>3.5</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="29">
-        <v>2.5</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="29">
-        <v>3.5</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="29">
-        <v>1</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="21" t="s">
+      <c r="H37" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="29">
-        <v>1</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="29">
-        <v>1</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="29">
-        <v>0.25</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-    </row>
-    <row r="37" spans="2:8">
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-    </row>
-    <row r="38" spans="2:8">
+      <c r="C38" s="21" t="s">
+        <v>169</v>
+      </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
@@ -4685,178 +4962,310 @@
       <c r="H38" s="21"/>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="25" t="s">
-        <v>150</v>
-      </c>
+      <c r="B39" s="47"/>
       <c r="C39" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="29">
+        <v>172</v>
+      </c>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="47"/>
+      <c r="C40" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="47"/>
+      <c r="C41" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="47"/>
+      <c r="C42" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="28">
         <v>0.5</v>
       </c>
-      <c r="H39" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8">
-      <c r="B40" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="29">
+      <c r="H43" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="48"/>
+      <c r="C44" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="28">
         <v>0.5</v>
       </c>
-      <c r="H40" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="29">
+      <c r="H44" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="48"/>
+      <c r="C45" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="28">
         <v>0.5</v>
       </c>
-      <c r="H41" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="33"/>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="33"/>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="33"/>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="34"/>
+      <c r="H45" s="28" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="34"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="21" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="35"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="21" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="35"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="21" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="49" spans="2:3">
-      <c r="B49" s="36"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="21" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="B50" s="36"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="21" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="51" spans="2:3">
-      <c r="B51" s="37"/>
+      <c r="B51" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="52" spans="2:3">
-      <c r="B52" s="37"/>
-      <c r="C52" s="26"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="21" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="53" spans="2:3">
-      <c r="B53" s="38"/>
+      <c r="B53" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="54" spans="2:3">
-      <c r="B54" s="38"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="21" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="55" spans="2:3">
-      <c r="B55" s="38"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="21" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="56" spans="2:3">
-      <c r="B56" s="38"/>
+      <c r="B56" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="57" spans="2:3">
-      <c r="B57" s="39"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="21" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="58" spans="2:3">
-      <c r="B58" s="39"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="21" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="59" spans="2:3">
-      <c r="B59" s="39"/>
+      <c r="B59" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="60" spans="2:3">
-      <c r="B60" s="39"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="25" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="61" spans="2:3">
-      <c r="B61" s="40"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="21" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="62" spans="2:3">
-      <c r="B62" s="40"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="21" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="63" spans="2:3">
-      <c r="B63" s="40"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="21" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="64" spans="2:3">
-      <c r="B64" s="40"/>
-      <c r="C64" s="53"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="21" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="32"/>
+      <c r="B65" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="32"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="44"/>
+      <c r="C67" s="21" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="68" spans="2:8">
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="42" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="69" spans="2:8">
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
+      <c r="B69" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="70" spans="2:8">
+      <c r="B70" s="51"/>
+      <c r="C70" s="21" t="s">
+        <v>158</v>
+      </c>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
       <c r="G70" s="21"/>
       <c r="H70" s="21"/>
     </row>
+    <row r="71" spans="2:8">
+      <c r="B71" s="51"/>
+      <c r="C71" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+    </row>
+    <row r="72" spans="2:8">
+      <c r="B72" s="51"/>
+      <c r="C72" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+    </row>
+    <row r="73" spans="2:8">
+      <c r="B73" s="51"/>
+      <c r="C73" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C2:H67" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H67">
-      <sortCondition ref="C2:C67"/>
+  <autoFilter ref="C2:H69" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H69">
+      <sortCondition ref="C2:C69"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D35 D39:D67" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D37 D43:D69" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E35 E39:E67" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E37 E43:E69" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H35 H39:H67" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H37 H43:H69" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4866,6 +5275,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5100,27 +5529,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5137,23 +5565,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7038D3EF-3DE5-465B-BFF3-9F3EE35893AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2349E2C-4FE1-4E9A-AACC-A080F72B45D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$70</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="216">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1392,16 +1392,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>操作説明</t>
-    <rPh sb="0" eb="2">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>キーマウ・パッド対応（余裕あれば）</t>
     <rPh sb="8" eb="10">
       <t>タイオウ</t>
@@ -1529,10 +1519,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3Dサウンド（FPSだしあってもいいかも）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>設定画面（少なくとも感度設定はいるかも）</t>
     <rPh sb="0" eb="4">
       <t>セッテイガメン</t>
@@ -1595,6 +1581,60 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステータス管理（HPとか）</t>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここは何ステージつくるかによるが、ステージ１以外はアルファでいいと思う</t>
+    <rPh sb="3" eb="4">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明（プレイ画面）</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明（メニューから）余裕あれば</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dサウンド（FPSだしゲーム性的にあってもいいかも）</t>
+    <rPh sb="15" eb="17">
+      <t>セイテキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4067,7 +4107,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F99)</f>
+        <f>SUM(作業工数見積もり!F3:F100)</f>
         <v>31.75</v>
       </c>
     </row>
@@ -4254,7 +4294,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L73"/>
+  <dimension ref="A2:L74"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
@@ -4303,7 +4343,7 @@
         <v>140</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>18</v>
@@ -4319,7 +4359,7 @@
       </c>
       <c r="K3" s="21">
         <f>SUM(K4,K5,K6)</f>
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:12">
@@ -4331,7 +4371,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="F4" s="28">
         <v>0.25</v>
@@ -4343,8 +4383,8 @@
         <v>126</v>
       </c>
       <c r="K4" s="39">
-        <f>COUNTIF(E3:E68,J4)</f>
-        <v>23</v>
+        <f>COUNTIF(E3:E69,J4)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -4368,8 +4408,8 @@
         <v>1</v>
       </c>
       <c r="K5" s="39">
-        <f>COUNTIF(E3:E68,J5)</f>
-        <v>9</v>
+        <f>COUNTIF(E3:E69,J5)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -4380,10 +4420,10 @@
         <v>176</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F6" s="28">
         <v>0.5</v>
@@ -4395,7 +4435,7 @@
         <v>127</v>
       </c>
       <c r="K6" s="39">
-        <f>COUNTIF(E3:E68,J6)</f>
+        <f>COUNTIF(E3:E69,J6)</f>
         <v>1</v>
       </c>
     </row>
@@ -4404,6 +4444,12 @@
       <c r="C7" s="21" t="s">
         <v>175</v>
       </c>
+      <c r="D7" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="J7" s="37"/>
       <c r="K7" s="39"/>
     </row>
@@ -4416,7 +4462,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F8" s="28">
         <v>0.25</v>
@@ -4428,7 +4474,7 @@
         <v>35</v>
       </c>
       <c r="K8" s="39">
-        <f>COUNTIF(H3:H68,J8)</f>
+        <f>COUNTIF(H3:H69,J8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="40">
@@ -4442,10 +4488,10 @@
         <v>164</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F9" s="28">
         <v>0.5</v>
@@ -4457,12 +4503,12 @@
         <v>134</v>
       </c>
       <c r="K9" s="39">
-        <f>COUNTIF(H3:H68,J9)</f>
+        <f>COUNTIF(H3:H69,J9)</f>
         <v>33</v>
       </c>
       <c r="L9" s="31">
         <f>(K9+K10)/K3</f>
-        <v>1</v>
+        <v>0.4925373134328358</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -4471,7 +4517,7 @@
         <v>165</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>34</v>
@@ -4486,7 +4532,7 @@
         <v>135</v>
       </c>
       <c r="K10" s="21">
-        <f>COUNTIF(H3:H68,J10)</f>
+        <f>COUNTIF(H3:H69,J10)</f>
         <v>0</v>
       </c>
     </row>
@@ -4496,7 +4542,7 @@
         <v>166</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>34</v>
@@ -4519,7 +4565,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F12" s="28">
         <v>1</v>
@@ -4531,7 +4577,7 @@
         <v>136</v>
       </c>
       <c r="K12" s="21">
-        <f>SUM(F3:F68)</f>
+        <f>SUM(F3:F69)</f>
         <v>31.75</v>
       </c>
     </row>
@@ -4544,7 +4590,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F13" s="28">
         <v>2</v>
@@ -4565,6 +4611,12 @@
       <c r="C14" s="21" t="s">
         <v>177</v>
       </c>
+      <c r="D14" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="J14" s="38"/>
     </row>
     <row r="15" spans="2:12">
@@ -4576,7 +4628,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F15" s="28">
         <v>3</v>
@@ -4595,7 +4647,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F16" s="28">
         <v>0.5</v>
@@ -4613,7 +4665,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F17" s="28">
         <v>1.5</v>
@@ -4631,7 +4683,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F18" s="28">
         <v>2.5</v>
@@ -4645,6 +4697,12 @@
       <c r="C19" s="21" t="s">
         <v>150</v>
       </c>
+      <c r="D19" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="45"/>
@@ -4655,7 +4713,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F20" s="28">
         <v>3.5</v>
@@ -4724,7 +4782,7 @@
         <v>153</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>34</v>
@@ -4742,10 +4800,10 @@
         <v>157</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F25" s="28">
         <v>0.5</v>
@@ -4763,7 +4821,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F26" s="28">
         <v>0.5</v>
@@ -4816,10 +4874,10 @@
         <v>155</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F29" s="28">
         <v>1</v>
@@ -4834,7 +4892,7 @@
         <v>151</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E30" s="28" t="s">
         <v>34</v>
@@ -4849,10 +4907,10 @@
     <row r="31" spans="2:8">
       <c r="B31" s="46"/>
       <c r="C31" s="21" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E31" s="28" t="s">
         <v>34</v>
@@ -4870,10 +4928,10 @@
         <v>146</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F32" s="28">
         <v>0.5</v>
@@ -4891,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F33" s="28">
         <v>0.5</v>
@@ -4923,17 +4981,29 @@
       <c r="C35" s="21" t="s">
         <v>183</v>
       </c>
+      <c r="D35" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="46"/>
       <c r="C36" s="21" t="s">
         <v>167</v>
       </c>
+      <c r="D36" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="46"/>
       <c r="C37" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>9</v>
@@ -4955,8 +5025,12 @@
       <c r="C38" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="D38" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="21"/>
@@ -4966,8 +5040,12 @@
       <c r="C39" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
@@ -4977,8 +5055,12 @@
       <c r="C40" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
+      <c r="D40" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="21"/>
@@ -4988,8 +5070,12 @@
       <c r="C41" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
+      <c r="D41" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
@@ -4999,6 +5085,12 @@
       <c r="C42" s="21" t="s">
         <v>158</v>
       </c>
+      <c r="D42" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="48" t="s">
@@ -5061,175 +5153,327 @@
       <c r="C46" s="21" t="s">
         <v>160</v>
       </c>
+      <c r="D46" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="48"/>
       <c r="C47" s="21" t="s">
         <v>178</v>
       </c>
+      <c r="D47" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="48"/>
       <c r="C48" s="21" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="49" spans="2:3">
+      <c r="D48" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="B49" s="48"/>
       <c r="C49" s="21" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="50" spans="2:3">
+      <c r="D49" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="B50" s="48"/>
       <c r="C50" s="21" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="51" spans="2:3">
+      <c r="D50" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="21" t="s">
+        <v>212</v>
+      </c>
       <c r="B51" s="49" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3">
+        <v>208</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="B52" s="49"/>
       <c r="C52" s="21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3">
+        <v>209</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="B53" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3">
+      <c r="D53" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="B54" s="50"/>
       <c r="C54" s="21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3">
+        <v>194</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="B55" s="50"/>
       <c r="C55" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3">
+        <v>193</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="B56" s="29" t="s">
         <v>184</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3">
+        <v>213</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="B57" s="29"/>
       <c r="C57" s="21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3">
+        <v>214</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="B58" s="29"/>
       <c r="C58" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="B59" s="29"/>
+      <c r="C59" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="B60" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="C60" s="21" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="59" spans="2:3">
-      <c r="B59" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="C59" s="21" t="s">
+      <c r="D60" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="B61" s="43"/>
+      <c r="C61" s="25" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="60" spans="2:3">
-      <c r="B60" s="43"/>
-      <c r="C60" s="25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3">
-      <c r="B61" s="43"/>
-      <c r="C61" s="21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3">
+      <c r="D61" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="B62" s="43"/>
       <c r="C62" s="21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3">
+        <v>188</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="B63" s="43"/>
       <c r="C63" s="21" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3">
+        <v>195</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="B64" s="43"/>
       <c r="C64" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="43"/>
+      <c r="C65" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
+      <c r="B66" s="44" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="44" t="s">
+      <c r="C66" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="44"/>
-      <c r="C66" s="21" t="s">
-        <v>201</v>
+      <c r="D66" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" s="44"/>
       <c r="C67" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" s="44"/>
-      <c r="C68" s="42" t="s">
+      <c r="C68" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="44"/>
+      <c r="C69" s="42" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>205</v>
+      <c r="D69" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="51"/>
+      <c r="B70" s="51" t="s">
+        <v>202</v>
+      </c>
       <c r="C70" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
+        <v>203</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" s="51"/>
       <c r="C71" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
+        <v>158</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F71" s="21"/>
       <c r="G71" s="21"/>
       <c r="H71" s="21"/>
@@ -5237,10 +5481,14 @@
     <row r="72" spans="2:8">
       <c r="B72" s="51"/>
       <c r="C72" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
+        <v>204</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>18</v>
+      </c>
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
@@ -5248,24 +5496,45 @@
     <row r="73" spans="2:8">
       <c r="B73" s="51"/>
       <c r="C73" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+    </row>
+    <row r="74" spans="2:8">
+      <c r="B74" s="51"/>
+      <c r="C74" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H69" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H69">
-      <sortCondition ref="C2:C69"/>
+  <autoFilter ref="C2:H70" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H70">
+      <sortCondition ref="C2:C70"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D37 D43:D69" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D74" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E37 E43:E69" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E74" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H37 H43:H69" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H37 H43:H70" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5275,26 +5544,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -5529,26 +5778,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0A0972-5393-459A-8603-138D87B70161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5565,4 +5815,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\genki\Documents\GitHub\koukiteam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2349E2C-4FE1-4E9A-AACC-A080F72B45D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60442848-B307-4AE7-B505-BD522AB4B586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="810" windowWidth="26025" windowHeight="14460" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1125_元データ" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1125_元データ'!$B$2:$G$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$C$2:$H$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">作業工数見積もり!$A$2:$I$78</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="230">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
     <phoneticPr fontId="1"/>
@@ -1596,19 +1596,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ここは何ステージつくるかによるが、ステージ１以外はアルファでいいと思う</t>
-    <rPh sb="3" eb="4">
-      <t>ナン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>操作説明（プレイ画面）</t>
     <rPh sb="0" eb="2">
       <t>ソウサ</t>
@@ -1635,6 +1622,129 @@
     <t>3Dサウンド（FPSだしゲーム性的にあってもいいかも）</t>
     <rPh sb="15" eb="17">
       <t>セイテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当者</t>
+    <rPh sb="0" eb="3">
+      <t>タントウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ数はプロト終わるまで様子見にする</t>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヨウスミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福田</t>
+    <rPh sb="0" eb="2">
+      <t>フクダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>久保田</t>
+    <rPh sb="0" eb="3">
+      <t>クボタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>玉利</t>
+    <rPh sb="0" eb="2">
+      <t>タマリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リプレイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松本</t>
+    <rPh sb="0" eb="2">
+      <t>マツモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内でのスコア表示</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>撃破数表示</t>
+    <rPh sb="0" eb="5">
+      <t>ゲキハスウヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここは何ステージつくるかによるが、簡易的なステージを作成し、以降はアルファでいいと思う</t>
+    <rPh sb="3" eb="4">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>カンイテキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松本</t>
+    <rPh sb="0" eb="2">
+      <t>マツモト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リプレイの再生</t>
+    <rPh sb="5" eb="7">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福田</t>
+    <rPh sb="0" eb="2">
+      <t>フクダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>久保田</t>
+    <rPh sb="0" eb="3">
+      <t>クボタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>廣田</t>
+    <rPh sb="0" eb="2">
+      <t>ヒロタ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2028,6 +2138,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF003399"/>
       <color rgb="FF9933FF"/>
       <color rgb="FF66FFFF"/>
       <color rgb="FFFF99FF"/>
@@ -2037,7 +2148,6 @@
       <color rgb="FF33CCFF"/>
       <color rgb="FF99FF33"/>
       <color rgb="FFCC9900"/>
-      <color rgb="FFFF99CC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2448,7 +2558,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4107,7 +4217,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F3:F100)</f>
+        <f>SUM(作業工数見積もり!F3:F104)</f>
         <v>31.75</v>
       </c>
     </row>
@@ -4151,7 +4261,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4294,7 +4404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L74"/>
+  <dimension ref="A2:M78"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="32.75" style="21" bestFit="1" customWidth="1"/>
@@ -4312,7 +4422,7 @@
     <col min="14" max="16384" width="9" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:13">
       <c r="B2" s="26" t="s">
         <v>129</v>
       </c>
@@ -4334,8 +4444,11 @@
       <c r="H2" s="27" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="3" spans="2:12">
+      <c r="I2" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
       <c r="B3" s="43" t="s">
         <v>139</v>
       </c>
@@ -4354,15 +4467,15 @@
       <c r="H3" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="K3" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="21">
-        <f>SUM(K4,K5,K6)</f>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
+      <c r="L3" s="21">
+        <f>SUM(L4,L5,L6)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
       <c r="B4" s="43"/>
       <c r="C4" s="21" t="s">
         <v>141</v>
@@ -4379,15 +4492,15 @@
       <c r="H4" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="K4" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="K4" s="39">
-        <f>COUNTIF(E3:E69,J4)</f>
+      <c r="L4" s="39">
+        <f>COUNTIF(E3:E78,K4)</f>
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:13">
       <c r="B5" s="43"/>
       <c r="C5" s="21" t="s">
         <v>142</v>
@@ -4404,15 +4517,15 @@
       <c r="H5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="K5" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="39">
-        <f>COUNTIF(E3:E69,J5)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
+      <c r="L5" s="39">
+        <f>COUNTIF(E3:E78,K5)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
       <c r="B6" s="44" t="s">
         <v>161</v>
       </c>
@@ -4431,15 +4544,18 @@
       <c r="H6" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="I6" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="K6" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="39">
-        <f>COUNTIF(E3:E69,J6)</f>
+      <c r="L6" s="39">
+        <f>COUNTIF(E3:E73,K6)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:13">
       <c r="B7" s="44"/>
       <c r="C7" s="21" t="s">
         <v>175</v>
@@ -4450,10 +4566,16 @@
       <c r="E7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="39"/>
-    </row>
-    <row r="8" spans="2:12">
+      <c r="H7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="L7" s="39"/>
+    </row>
+    <row r="8" spans="2:13">
       <c r="B8" s="44"/>
       <c r="C8" s="21" t="s">
         <v>162</v>
@@ -4462,7 +4584,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F8" s="28">
         <v>0.25</v>
@@ -4470,19 +4592,19 @@
       <c r="H8" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="K8" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="39">
-        <f>COUNTIF(H3:H69,J8)</f>
+      <c r="L8" s="39">
+        <f>COUNTIF(H3:H73,K8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="40">
-        <f>K8/K3</f>
+      <c r="M8" s="40">
+        <f>L8/L3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:13">
       <c r="B9" s="44"/>
       <c r="C9" s="21" t="s">
         <v>164</v>
@@ -4499,19 +4621,22 @@
       <c r="H9" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="I9" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="K9" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="K9" s="39">
-        <f>COUNTIF(H3:H69,J9)</f>
-        <v>33</v>
-      </c>
-      <c r="L9" s="31">
-        <f>(K9+K10)/K3</f>
-        <v>0.4925373134328358</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
+      <c r="L9" s="39">
+        <f>COUNTIF(H3:H73,K9)</f>
+        <v>71</v>
+      </c>
+      <c r="M9" s="31">
+        <f>(L9+L10)/L3</f>
+        <v>0.94666666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
       <c r="B10" s="44"/>
       <c r="C10" s="21" t="s">
         <v>165</v>
@@ -4520,7 +4645,7 @@
         <v>17</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F10" s="28">
         <v>0.5</v>
@@ -4528,15 +4653,15 @@
       <c r="H10" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="K10" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="K10" s="21">
-        <f>COUNTIF(H3:H69,J10)</f>
+      <c r="L10" s="21">
+        <f>COUNTIF(H3:H73,K10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:13">
       <c r="B11" s="44"/>
       <c r="C11" s="21" t="s">
         <v>166</v>
@@ -4545,7 +4670,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F11" s="28">
         <v>0.5</v>
@@ -4554,7 +4679,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:13">
       <c r="B12" s="45" t="s">
         <v>143</v>
       </c>
@@ -4573,15 +4698,18 @@
       <c r="H12" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="I12" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="K12" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="K12" s="21">
-        <f>SUM(F3:F69)</f>
+      <c r="L12" s="21">
+        <f>SUM(F3:F73)</f>
         <v>31.75</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:13">
       <c r="B13" s="45"/>
       <c r="C13" s="21" t="s">
         <v>145</v>
@@ -4598,15 +4726,18 @@
       <c r="H13" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="J13" s="38" t="s">
+      <c r="I13" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="K13" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="21">
-        <f>8*K12</f>
+      <c r="L13" s="21">
+        <f>8*L12</f>
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:13">
       <c r="B14" s="45"/>
       <c r="C14" s="21" t="s">
         <v>177</v>
@@ -4617,9 +4748,15 @@
       <c r="E14" s="28" t="s">
         <v>34</v>
       </c>
+      <c r="H14" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>218</v>
+      </c>
       <c r="J14" s="38"/>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:13">
       <c r="B15" s="45"/>
       <c r="C15" s="21" t="s">
         <v>146</v>
@@ -4636,9 +4773,12 @@
       <c r="H15" s="28" t="s">
         <v>138</v>
       </c>
+      <c r="I15" s="21" t="s">
+        <v>218</v>
+      </c>
       <c r="J15" s="38"/>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:13">
       <c r="B16" s="45"/>
       <c r="C16" s="21" t="s">
         <v>147</v>
@@ -4656,7 +4796,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:9">
       <c r="B17" s="45"/>
       <c r="C17" s="21" t="s">
         <v>148</v>
@@ -4674,7 +4814,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:9">
       <c r="B18" s="45"/>
       <c r="C18" s="21" t="s">
         <v>149</v>
@@ -4692,7 +4832,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:9">
       <c r="B19" s="45"/>
       <c r="C19" s="21" t="s">
         <v>150</v>
@@ -4703,8 +4843,14 @@
       <c r="E19" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="2:8">
+      <c r="H19" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="45"/>
       <c r="C20" s="21" t="s">
         <v>180</v>
@@ -4722,7 +4868,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:9">
       <c r="B21" s="45"/>
       <c r="C21" s="21" t="s">
         <v>160</v>
@@ -4739,8 +4885,11 @@
       <c r="H21" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="22" spans="2:8">
+      <c r="I21" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="45"/>
       <c r="C22" s="21" t="s">
         <v>151</v>
@@ -4757,8 +4906,11 @@
       <c r="H22" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="23" spans="2:8">
+      <c r="I22" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="45"/>
       <c r="C23" s="21" t="s">
         <v>152</v>
@@ -4776,7 +4928,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:9">
       <c r="B24" s="45"/>
       <c r="C24" s="21" t="s">
         <v>153</v>
@@ -4793,8 +4945,11 @@
       <c r="H24" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="I24" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="45"/>
       <c r="C25" s="21" t="s">
         <v>157</v>
@@ -4812,7 +4967,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:9">
       <c r="B26" s="45"/>
       <c r="C26" s="21" t="s">
         <v>158</v>
@@ -4830,7 +4985,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:9">
       <c r="B27" s="46" t="s">
         <v>154</v>
       </c>
@@ -4849,8 +5004,11 @@
       <c r="H27" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="2:8">
+      <c r="I27" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="B28" s="46"/>
       <c r="C28" s="21" t="s">
         <v>156</v>
@@ -4867,8 +5025,11 @@
       <c r="H28" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="29" spans="2:8">
+      <c r="I28" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="B29" s="46"/>
       <c r="C29" s="21" t="s">
         <v>155</v>
@@ -4885,8 +5046,11 @@
       <c r="H29" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="2:8">
+      <c r="I29" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="B30" s="46"/>
       <c r="C30" s="21" t="s">
         <v>151</v>
@@ -4903,8 +5067,11 @@
       <c r="H30" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="I30" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" s="46"/>
       <c r="C31" s="21" t="s">
         <v>211</v>
@@ -4921,8 +5088,11 @@
       <c r="H31" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="2:8">
+      <c r="I31" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" s="46"/>
       <c r="C32" s="21" t="s">
         <v>146</v>
@@ -4940,7 +5110,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:9">
       <c r="B33" s="46"/>
       <c r="C33" s="21" t="s">
         <v>159</v>
@@ -4958,7 +5128,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:9">
       <c r="B34" s="46"/>
       <c r="C34" s="21" t="s">
         <v>163</v>
@@ -4975,8 +5145,11 @@
       <c r="H34" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="I34" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
       <c r="B35" s="46"/>
       <c r="C35" s="21" t="s">
         <v>183</v>
@@ -4987,8 +5160,11 @@
       <c r="E35" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="H35" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
       <c r="B36" s="46"/>
       <c r="C36" s="21" t="s">
         <v>167</v>
@@ -4999,8 +5175,14 @@
       <c r="E36" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="2:8">
+      <c r="H36" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
       <c r="B37" s="46"/>
       <c r="C37" s="21" t="s">
         <v>190</v>
@@ -5017,8 +5199,11 @@
       <c r="H37" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="38" spans="2:8">
+      <c r="I37" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
       <c r="B38" s="47" t="s">
         <v>168</v>
       </c>
@@ -5033,9 +5218,11 @@
       </c>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39" spans="2:8">
+      <c r="H38" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
       <c r="B39" s="47"/>
       <c r="C39" s="21" t="s">
         <v>172</v>
@@ -5048,9 +5235,11 @@
       </c>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-    </row>
-    <row r="40" spans="2:8">
+      <c r="H39" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
       <c r="B40" s="47"/>
       <c r="C40" s="21" t="s">
         <v>147</v>
@@ -5063,9 +5252,11 @@
       </c>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-    </row>
-    <row r="41" spans="2:8">
+      <c r="H40" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
       <c r="B41" s="47"/>
       <c r="C41" s="21" t="s">
         <v>182</v>
@@ -5078,9 +5269,11 @@
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="H41" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
       <c r="B42" s="47"/>
       <c r="C42" s="21" t="s">
         <v>158</v>
@@ -5091,8 +5284,11 @@
       <c r="E42" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="2:8">
+      <c r="H42" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
       <c r="B43" s="48" t="s">
         <v>170</v>
       </c>
@@ -5111,8 +5307,11 @@
       <c r="H43" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="44" spans="2:8">
+      <c r="I43" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
       <c r="B44" s="48"/>
       <c r="C44" s="21" t="s">
         <v>173</v>
@@ -5129,8 +5328,11 @@
       <c r="H44" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="45" spans="2:8">
+      <c r="I44" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
       <c r="B45" s="48"/>
       <c r="C45" s="21" t="s">
         <v>179</v>
@@ -5147,8 +5349,11 @@
       <c r="H45" s="28" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="46" spans="2:8">
+      <c r="I45" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
       <c r="B46" s="48"/>
       <c r="C46" s="21" t="s">
         <v>160</v>
@@ -5159,8 +5364,14 @@
       <c r="E46" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="2:8">
+      <c r="H46" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
       <c r="B47" s="48"/>
       <c r="C47" s="21" t="s">
         <v>178</v>
@@ -5171,8 +5382,14 @@
       <c r="E47" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="H47" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I47" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
       <c r="B48" s="48"/>
       <c r="C48" s="21" t="s">
         <v>174</v>
@@ -5183,8 +5400,14 @@
       <c r="E48" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="H48" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="B49" s="48"/>
       <c r="C49" s="21" t="s">
         <v>181</v>
@@ -5195,8 +5418,11 @@
       <c r="E49" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="H49" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="B50" s="48"/>
       <c r="C50" s="21" t="s">
         <v>158</v>
@@ -5207,10 +5433,13 @@
       <c r="E50" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="H50" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="21" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B51" s="49" t="s">
         <v>207</v>
@@ -5224,8 +5453,17 @@
       <c r="E51" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="H51" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="21" t="s">
+        <v>216</v>
+      </c>
       <c r="B52" s="49"/>
       <c r="C52" s="21" t="s">
         <v>209</v>
@@ -5236,8 +5474,14 @@
       <c r="E52" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="H52" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I52" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="B53" s="50" t="s">
         <v>191</v>
       </c>
@@ -5250,8 +5494,14 @@
       <c r="E53" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="H53" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I53" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="B54" s="50"/>
       <c r="C54" s="21" t="s">
         <v>194</v>
@@ -5262,61 +5512,91 @@
       <c r="E54" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="H54" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="B55" s="50"/>
       <c r="C55" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E55" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="B56" s="29" t="s">
+      <c r="H55" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="B56" s="50"/>
+      <c r="C56" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="B57" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="C56" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" s="29"/>
       <c r="C57" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E57" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="H57" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="B58" s="29"/>
       <c r="C58" s="21" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E58" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="H58" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="B59" s="29"/>
       <c r="C59" s="21" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D59" s="28" t="s">
         <v>25</v>
@@ -5324,218 +5604,346 @@
       <c r="E59" s="28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="B60" s="43" t="s">
+      <c r="H59" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="B60" s="29"/>
+      <c r="C60" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I60" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="B61" s="29"/>
+      <c r="C61" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="B62" s="29"/>
+      <c r="C62" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I62" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="B63" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C63" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="D60" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="B61" s="43"/>
-      <c r="C61" s="25" t="s">
+      <c r="D63" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I63" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="B64" s="43"/>
+      <c r="C64" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="D64" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="B62" s="43"/>
-      <c r="C62" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="B63" s="43"/>
-      <c r="C63" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="B64" s="43"/>
-      <c r="C64" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>9</v>
-      </c>
       <c r="E64" s="28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="65" spans="2:8">
+      <c r="H64" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I64" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9">
       <c r="B65" s="43"/>
       <c r="C65" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I65" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9">
+      <c r="B66" s="43"/>
+      <c r="C66" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I66" s="21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="43"/>
+      <c r="C67" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I67" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="B68" s="43"/>
+      <c r="C68" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="I68" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" s="43"/>
+      <c r="C69" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D69" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E65" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8">
-      <c r="B66" s="44" t="s">
+      <c r="E69" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="B70" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C70" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="D66" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="44"/>
-      <c r="C67" s="21" t="s">
+      <c r="D70" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="B71" s="44"/>
+      <c r="C71" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="D67" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8">
-      <c r="B68" s="44"/>
-      <c r="C68" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="D68" s="28" t="s">
+      <c r="D71" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="B72" s="44"/>
+      <c r="C72" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E68" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" s="44"/>
-      <c r="C69" s="42" t="s">
+      <c r="E72" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="44"/>
+      <c r="C73" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="D69" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8">
-      <c r="B70" s="51" t="s">
+      <c r="D73" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C74" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="D70" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8">
-      <c r="B71" s="51"/>
-      <c r="C71" s="21" t="s">
+      <c r="D74" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="51"/>
+      <c r="C75" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D71" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-    </row>
-    <row r="72" spans="2:8">
-      <c r="B72" s="51"/>
-      <c r="C72" s="21" t="s">
+      <c r="D75" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9">
+      <c r="B76" s="51"/>
+      <c r="C76" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="D72" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-    </row>
-    <row r="73" spans="2:8">
-      <c r="B73" s="51"/>
-      <c r="C73" s="21" t="s">
+      <c r="D76" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9">
+      <c r="B77" s="51"/>
+      <c r="C77" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="D73" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="B74" s="51"/>
-      <c r="C74" s="21" t="s">
+      <c r="D77" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9">
+      <c r="B78" s="51"/>
+      <c r="C78" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="D74" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="28" t="s">
-        <v>18</v>
+      <c r="D78" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="28" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H70" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H70">
-      <sortCondition ref="C2:C70"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:I78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D74" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H78" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+      <formula1>"未着手,作業中,完了"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D78" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E74" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E78" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H37 H43:H70" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
-      <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
